--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,73 +541,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2040328252468940931</t>
+          <t>2042145058133307907</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040328252468940931</t>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>TS Aswani Kumar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:18 AM UTC</t>
+          <t>Apr 9, 2026 · 7:38 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-04T07:18:00Z</t>
+          <t>2026-04-09T07:38:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +625,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2040327735621656747</t>
+          <t>2041809616133316853</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327735621656747</t>
+          <t>https://x.com/Nauphal/status/2041809616133316853</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/Nauphal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>Nauphal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>Nauphal LLC SP</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>Sent DM. Please respond.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>Sent DM. Please respond.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -675,17 +675,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 8, 2026 · 9:25 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-08T09:25:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -709,73 +709,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2040327679250153863</t>
+          <t>2041770828887683094</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327679250153863</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770828887683094</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>@emiratesislamic I'm posting here because i don't have an option out, SM team please look into it.》》</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m posting here because i don&amp;#39;t have an option out, SM team please look into it.》》</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 8, 2026 · 6:51 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-08T06:51:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -793,89 +793,69 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2040280370994889131</t>
+          <t>2041770661786612135</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111/status/2040280370994889131</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770661786612135</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mubi_111</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mubarak Albreiki</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+          <t>@emiratesislamic also i was told that the money on hold is due to my end of service. Now they're changing the story. As a customer I'm going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; also i was told that the money on hold is due to my end of service. Now they&amp;#39;re changing the story. As a customer I&amp;#39;m going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 4:08 AM UTC</t>
+          <t>Apr 8, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-04T04:08:00Z</t>
+          <t>2026-04-08T06:50:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -888,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>633</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -897,89 +877,69 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2040271345058209886</t>
+          <t>2041770214564753782</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111/status/2040271345058209886</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770214564753782</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mubi_111</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mubarak Albreiki</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+          <t>@emiratesislamic the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Apr 4</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 3:32 AM UTC</t>
+          <t>Apr 8, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-04T03:32:00Z</t>
+          <t>2026-04-08T06:48:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -992,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>589</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1001,71 +961,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2040328252468940931</t>
+          <t>2041769750137864312</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040328252468940931</t>
+          <t>https://x.com/Renn_Stan_Lee/status/2041769750137864312</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>Renn_Stan_Lee</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>Rennn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>@emiratesislamic I'm facing a terrible experience with EI. I've been contacting customer service back &amp; forth for the past 2 months for the end of service hold amount in my account. 
+I've been told that the hold amount would be released soon, even received an email mentioning《《</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>قمة بأر سال ايمييل و تواصل مع خدمة العملاء من تاريخ 28/7/2025 وحتى الان لايوجد رد غير نعذر على التأخير</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m facing a terrible experience with EI. I&amp;#39;ve been contacting customer service back &amp;amp; forth for the past 2 months for the end of service hold amount in my account. 
+I&amp;#39;ve been told that the hold amount would be released soon, even received an email mentioning《《</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:18 AM UTC</t>
+          <t>Apr 8, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-04T07:18:00Z</t>
+          <t>2026-04-08T06:46:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1076,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1085,43 +1047,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2040327735621656747</t>
+          <t>2041761819669492128</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327735621656747</t>
+          <t>https://x.com/Nauphal/status/2041761819669492128</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/Nauphal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>Nauphal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>Nauphal LLC SP</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>Hello, I haven't received any DM. No solution or response from other channels.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>Hello, I haven&amp;#39;t received any DM. No solution or response from other channels.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1130,28 +1092,28 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['Nauphal', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 8, 2026 · 6:15 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-08T06:15:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1160,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1169,82 +1131,82 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2040327679250153863</t>
+          <t>2041760360621818126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl/status/2040327679250153863</t>
+          <t>https://x.com/emiratesislamic/status/2041760360621818126</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/MatarAlAl</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MatarAlAl</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matar Al Ali</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1684083417095315456/H0Hb8BEQ_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>قام موظف البنك لديكم بالتواصل معي انني لم اقم بدفع الدفع المستحقة للبنك وانه يجب عليه ايداع المبلغ عن طرق آلة الايداع و وضع رقم التمويل والذي هو 1804235  وحاولة اخبره اني سأضع المبلغ في الحساب قال لي لا تستطيع فقمة بإيداع المبلغ  وحين سؤال البنك اخبرني انه لايضهر عندنا انك قمت</t>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 7:16 AM UTC</t>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-04T07:16:00Z</t>
+          <t>2026-04-08T06:09:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -1253,102 +1215,84 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2040280370994889131</t>
+          <t>2041757945084453281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111/status/2040280370994889131</t>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>mubi_111</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mubarak Albreiki</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 8</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 4, 2026 · 4:08 AM UTC</t>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-04T04:08:00Z</t>
+          <t>2026-04-08T06:00:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>633</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -1357,59 +1301,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2040271345058209886</t>
+          <t>2042152553400385940</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111/status/2040271345058209886</t>
+          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/mubi_111</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>mubi_111</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mubarak Albreiki</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028249565288423424/26duc-EC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-#بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
-تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
-هذا التصرف يثير الكثير من علامات الاستفهام:
-هل ما يتم عرضه للعملاء مجرد وعود غير دقيقة؟
-أين الشفافية في التعامل؟
-وكيف يُبنى قرار مالي على معلومات غير صحيحة؟
-ما حدث لا يُعتبر فقط خطأ بسيط، بل هو إخلال بالثقة ويدخل ضمن إطار التضليل في تقديم العروض.
-أطالب بنك الإمارات الإسلامي بتوضيح فوري وتصحيح هذا الوضع، والالتزام بما تم الاتفاق عليه دون أي تغيير أو تلاعب.
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شكوى"&gt;#شكوى&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حقوق_العملاء"&gt;#حقوق_العملاء&lt;/a&gt; #</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1418,41 +1346,2439 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
+          <t>['aswanikumartst5']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 8:08 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-09T08:08:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2042120326721523923</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-09T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2042120323168956518</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-09T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2041821273811034189</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041821273811034189</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-08T10:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2041821271319593215</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041821271319593215</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-08T10:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2041818196261372116</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041818196261372116</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:59:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2041803534602027153</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041803534602027153</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Dear customer, it looks like your profile settings may be restricting us from sending you a direct message. To assist you further, please send us a DM or contact us via email at customercareunit@emiratesislamic.ae with your registered details, and we will be happy to support you</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dear customer, it looks like your profile settings may be restricting us from sending you a direct message. To assist you further, please send us a DM or contact us via email at customercareunit@emiratesislamic.ae with your registered details, and we will be happy to support you</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['Nauphal']</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2041782777020829965</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041782777020829965</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['Renn_Stan_Lee']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-08T07:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2041760363436179910</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760363436179910</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2041760360621818126</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760360621818126</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
+📊 Profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2041760338308104592</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760338308104592</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2041760334214463800</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760334214463800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>استمتع بمعدلات ربح تنافسية مع تمويل السيارات من الإمارات الإسلامي.
+📊 معدلات ربح تبدأ من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+💳 برنامج الدفع الميسر %0 على نفقات البطاقة الائتمانية من الإمارات الإسلامي</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>استمتع بمعدلات ربح تنافسية مع تمويل السيارات من الإمارات الإسلامي.
+📊 معدلات ربح تبدأ من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
+💳 برنامج الدفع الميسر %0 على نفقات البطاقة الائتمانية من الإمارات الإسلامي</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2041757946946666925</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757946946666925</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2041757945084453281</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2041757941938725257</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757941938725257</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2041757939090829772</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757939090829772</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TS Aswani Kumar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-09T07:38:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2042120326721523923</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-09T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2041821273811034189</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041821273811034189</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 10:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-08T10:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2041809616133316853</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/Nauphal/status/2041809616133316853</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/Nauphal</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nauphal</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nauphal LLC SP</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1683523208643846149/pCig8bNs_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sent DM. Please respond.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sent DM. Please respond.</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Apr 4</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 4, 2026 · 3:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-04-04T03:32:00Z</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23شكوى', 'https://x.com/search?f=tweets&amp;q=%23حقوق_العملاء']</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>589</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 9:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2041770828887683094</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770828887683094</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I'm posting here because i don't have an option out, SM team please look into it.》》</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m posting here because i don&amp;#39;t have an option out, SM team please look into it.》》</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2041770661786612135</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770661786612135</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>@emiratesislamic also i was told that the money on hold is due to my end of service. Now they're changing the story. As a customer I'm going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; also i was told that the money on hold is due to my end of service. Now they&amp;#39;re changing the story. As a customer I&amp;#39;m going through this bizzarre experience for the past 2 months. Never faced something in my entire life with banking like this《《</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2041770214564753782</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041770214564753782</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>@emiratesislamic the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; the same. Then i receive a call and get an entire different story that it is some previous amount which was during the buyout. So its like numerous employees gave me false information including call recordings and email, i visited the branch as well and there《《</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:48:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2041769750137864312</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee/status/2041769750137864312</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Renn_Stan_Lee</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rennn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1470900878303395841/8wUx8wFh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I'm facing a terrible experience with EI. I've been contacting customer service back &amp; forth for the past 2 months for the end of service hold amount in my account. 
+I've been told that the hold amount would be released soon, even received an email mentioning《《</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I&amp;#39;m facing a terrible experience with EI. I&amp;#39;ve been contacting customer service back &amp;amp; forth for the past 2 months for the end of service hold amount in my account. 
+I&amp;#39;ve been told that the hold amount would be released soon, even received an email mentioning《《</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2041760363436179910</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760363436179910</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Valid until April 30 2026
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2041760338308104592</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041760338308104592</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>يسري لغاية 30 أبريل 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=auto_finance"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=auto_finance']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2041757946946666925</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757946946666925</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Discounts on flights and hotel bookings
+Airport lounge access, meet and greet services
+and much more.
+To know more visit &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2041757945084453281</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
+✔️Cashback and rewards on everyday spending
+✔️Valet parking and special discounts on dining 
+✔️Flexible payment options</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2041757941938725257</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757941938725257</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Apr 8</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-04-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,79 +541,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045744202651226430</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/mohmd_moh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>mohmd_moh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohamed Mohamed</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/581880425234059264/lFW7trTI_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 1:46 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T13:46:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -624,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -633,81 +629,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 1:20 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T13:20:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -715,10 +701,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -727,84 +713,2806 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever</t>
+          <t>https://x.com/gassann20203</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>firstdiver4ever</t>
+          <t>gassann20203</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>اماراتى وافتخر</t>
+          <t>gazan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1979011185929342976/BA4ftLDA_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 7:47 AM UTC</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-04-19T07:47:00Z</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['firstdiver4ever']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 9:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-20T09:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['mohmd_moh']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2046224051438526663</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>mohmd_moh</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mohamed Mohamed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/581880425234059264/lFW7trTI_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:46 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:46:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2046215734481834418</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>gassann20203</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>gazan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1979011185929342976/BA4ftLDA_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2046976426990268451</t>
+          <t>2047447622948901334</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806/status/2046976426990268451</t>
+          <t>https://x.com/gold_hadas/status/2047447622948901334</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UpendraS83806</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Upendra Singh</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Please check your inbox.</t>
+          <t>Emirates Islamic operating profit rises 7% to $299.52mln in Q1 zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Please check your inbox.</t>
+          <t>Emirates Islamic operating profit rises 7% to $299.52mln in Q1 &lt;a href="https://www.zawya.com/en/capital-markets/equities/emirates-islamic-operating-profit-rises-7-to-29952mln-in-q1-dn38tez1"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 3:36 PM UTC</t>
+          <t>Apr 23, 2026 · 10:48 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-22T15:36:00Z</t>
+          <t>2026-04-23T22:48:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://www.zawya.com/en/capital-markets/equities/emirates-islamic-operating-profit-rises-7-to-29952mln-in-q1-dn38tez1']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -625,12 +625,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2046831372824674407</t>
+          <t>2047287763796427063</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
+          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -656,20 +656,14 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-emiratesislamic.ae/en/Person…</t>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -679,23 +673,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 12:13 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-22T06:00:00Z</t>
+          <t>2026-04-23T12:13:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -708,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -717,51 +711,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2046882012129058966</t>
+          <t>2047271389288083759</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046882012129058966</t>
+          <t>https://x.com/royamoney/status/2047271389288083759</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/royamoney</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>royamoney</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>رؤيا مال وأعمال</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042189267682623488/fSkX4rxF_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
+          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -776,20 +762,16 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
+          <t>Apr 23, 2026 · 11:08 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-22T09:21:00Z</t>
+          <t>2026-04-23T11:08:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -800,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -809,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2046882010497524009</t>
+          <t>2047193753073402364</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046882010497524009</t>
+          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -840,14 +822,24 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>Your spending isn’t random… it has patterns.
+Check your last 10 transactions.
+Look for repeats, not amounts.
+You’ll quickly see what’s costing you the most, 
+it’s habits, not purchases.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>Your spending isn’t random… it has patterns.
+Check your last 10 transactions.
+Look for repeats, not amounts.
+You’ll quickly see what’s costing you the most, 
+it’s habits, not purchases.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -857,23 +849,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-22T09:21:00Z</t>
+          <t>2026-04-23T06:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -882,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -891,12 +887,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2046882007976698203</t>
+          <t>2047289060557824183</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046882007976698203</t>
+          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -922,20 +918,12 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
+          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -945,27 +933,23 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
+          <t>Apr 23, 2026 · 12:18 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-22T09:21:00Z</t>
+          <t>2026-04-23T12:18:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -974,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -983,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2046881064883249563</t>
+          <t>2047287763796427063</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046881064883249563</t>
+          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1014,20 +998,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1037,23 +1015,23 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+          <t>Apr 23, 2026 · 12:13 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-22T09:17:00Z</t>
+          <t>2026-04-23T12:13:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing']</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1066,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -1075,12 +1053,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2046881062899355911</t>
+          <t>2047249946475160040</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046881062899355911</t>
+          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1106,14 +1084,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
+&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1123,23 +1101,27 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+          <t>Apr 23, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-22T09:17:00Z</t>
+          <t>2026-04-23T09:43:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1148,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1157,12 +1139,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2046881060533727547</t>
+          <t>2047249884101673033</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046881060533727547</t>
+          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1188,20 +1170,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
+          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
+emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
+&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1211,23 +1187,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+          <t>Apr 23, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-22T09:17:00Z</t>
+          <t>2026-04-23T09:43:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
+          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1240,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -1249,12 +1225,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2046881058352746917</t>
+          <t>2047249881757085701</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046881058352746917</t>
+          <t>https://x.com/emiratesislamic/status/2047249881757085701</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1280,18 +1256,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1301,17 +1271,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
+          <t>Apr 23, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-22T09:17:00Z</t>
+          <t>2026-04-23T09:43:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1326,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>171</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -1335,12 +1305,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2046878598796112328</t>
+          <t>2047241499490807897</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046878598796112328</t>
+          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1385,32 +1355,32 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 9:07 AM UTC</t>
+          <t>Apr 23, 2026 · 9:09 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-22T09:07:00Z</t>
+          <t>2026-04-23T09:09:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1419,12 +1389,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2046861646031651319</t>
+          <t>2047193755975917822</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046861646031651319</t>
+          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1450,40 +1420,42 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>['mond33']</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 8:00 AM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-22T08:00:00Z</t>
+          <t>2026-04-23T06:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -1491,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -1503,12 +1475,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2046831372824674407</t>
+          <t>2047193753073402364</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
+          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1534,20 +1506,24 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-emiratesislamic.ae/en/Person…</t>
+          <t>Your spending isn’t random… it has patterns.
+Check your last 10 transactions.
+Look for repeats, not amounts.
+You’ll quickly see what’s costing you the most, 
+it’s habits, not purchases.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>Your spending isn’t random… it has patterns.
+Check your last 10 transactions.
+Look for repeats, not amounts.
+You’ll quickly see what’s costing you the most, 
+it’s habits, not purchases.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1557,23 +1533,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-22T06:00:00Z</t>
+          <t>2026-04-23T06:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1595,12 +1571,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2046831371042107554</t>
+          <t>2047193753073357199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046831371042107554</t>
+          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1626,16 +1602,20 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
+          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
+راجع آخر 10 معاملات لديك،
+وابحث عن التكرار لا عن المبالغ،
+وستكتشف سريعاً ما يستنزف أموالك أكثر.
+فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
+راجع آخر 10 معاملات لديك،
+وابحث عن التكرار لا عن المبالغ،
+وستكتشف سريعاً ما يستنزف أموالك أكثر.
+فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1645,25 +1625,21 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-22T06:00:00Z</t>
+          <t>2026-04-23T06:00:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>1</v>
       </c>
@@ -1674,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -1683,12 +1659,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2046831368349348321</t>
+          <t>2047249946475160040</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046831368349348321</t>
+          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1714,12 +1690,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
+          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
+          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
+&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1729,23 +1707,27 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-22T06:00:00Z</t>
+          <t>2026-04-23T09:43:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1754,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -1763,12 +1745,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2046831365216235900</t>
+          <t>2047249884101673033</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046831365216235900</t>
+          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1794,14 +1776,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>البقالة. المطاعم. التسوق.
-أنفق واحصل على المكافآت أينما كنت!</t>
+          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
+emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>البقالة. المطاعم. التسوق.
-أنفق واحصل على المكافآت أينما كنت!</t>
+          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
+&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1811,21 +1793,25 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-22T06:00:00Z</t>
+          <t>2026-04-23T09:43:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+        </is>
+      </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
@@ -1836,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1845,71 +1831,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2046976426990268451</t>
+          <t>2047193755975917822</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806/status/2046976426990268451</t>
+          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UpendraS83806</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Upendra Singh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Please check your inbox.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Please check your inbox.</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 · 3:36 PM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-22T15:36:00Z</t>
+          <t>2026-04-23T06:00:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -1920,799 +1908,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2046882012129058966</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046882012129058966</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2046882010497524009</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046882010497524009</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2046882007976698203</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046882007976698203</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2046881064883249563</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046881064883249563</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:17:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2046881062899355911</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046881062899355911</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:17:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2046881060533727547</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046881060533727547</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 9:17 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-04-22T09:17:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2046831372824674407</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046831372824674407</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Groceries. Dining. Shopping.
-Turn every swipe into rewards!
-Enjoy cashback and rewards, unlock travel perks, access lifestyle offers, and benefit from flexible payment options, with Emirates Islamic Credit Cards.
-To know more, visit:
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-04-22T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2046831371042107554</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046831371042107554</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>اجعل كل معاملة تجربة مالية ذكية تضيف قيمة لحياتك اليومية.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-04-22T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Cards/credit-cards?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc']</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2046831368349348321</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046831368349348321</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>استفد من استرداد نقدي ومكافآت على مشترياتك اليومية، وتمتع بمزايا سفر حصرية، وعروض مبتكرة تناسب اهتماماتك، مع خيارات دفع مرنة مصممة لتلبية احتياجاتك، عبر بطاقات ائتمان الإمارات الإسلامي.</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-04-22T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047447622948901334</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2047447622948901334</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Emirates Islamic operating profit rises 7% to $299.52mln in Q1 zawya.com/en/capital-markets…</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Emirates Islamic operating profit rises 7% to $299.52mln in Q1 &lt;a href="https://www.zawya.com/en/capital-markets/equities/emirates-islamic-operating-profit-rises-7-to-29952mln-in-q1-dn38tez1"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 10:48 PM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-23T22:48:00Z</t>
+          <t>2026-04-25T00:29:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://www.zawya.com/en/capital-markets/equities/emirates-islamic-operating-profit-rises-7-to-29952mln-in-q1-dn38tez1']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -625,12 +625,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -656,14 +656,22 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt;</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -673,23 +681,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 12:13 PM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-23T12:13:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -702,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -711,43 +719,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>royamoney</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رؤيا مال وأعمال</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042189267682623488/fSkX4rxF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic.</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic.</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -757,23 +771,23 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 11:08 AM UTC</t>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-23T11:08:00Z</t>
+          <t>2026-04-24T11:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -782,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -791,55 +805,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047193753073402364</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ABCinGCC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ABCinGCC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Arabian Business Community (ABC GCC)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on abc-gcc.net/News/1/395058
+#ABCNews #Profit #Banking #FinancialInstitution</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -849,23 +855,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 7:15 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T07:15:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -878,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -887,12 +893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,12 +924,20 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -933,21 +947,25 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 12:18 PM UTC</t>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-23T12:18:00Z</t>
+          <t>2026-04-24T06:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -958,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -967,12 +985,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -998,14 +1016,22 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt;</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1015,23 +1041,23 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 12:13 PM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-23T12:13:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23Investing']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1044,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1053,12 +1079,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1084,14 +1110,18 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-emiratesislamic.ae/en/news-a…</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1101,36 +1131,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T16:43:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1139,12 +1165,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1170,14 +1196,24 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-emiratesislamic.ae/ar/news-a…</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1187,27 +1223,27 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T16:42:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1216,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>49</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -1225,12 +1261,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249881757085701</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1256,12 +1292,16 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة.</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1271,17 +1311,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T16:42:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1296,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -1305,12 +1345,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1336,36 +1376,46 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['UpendraS83806']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:09 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-23T09:09:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1380,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -1389,12 +1439,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047193755975917822</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1420,14 +1470,14 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Terms &amp; condition apply.
+To know more, please visit emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1437,23 +1487,23 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1466,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1475,12 +1525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047193753073402364</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1506,24 +1556,24 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp; discounts
+Start them young!</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young!</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1533,27 +1583,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1562,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -1571,12 +1617,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047193753073357199</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1602,20 +1648,12 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1625,21 +1663,25 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
@@ -1650,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1659,12 +1701,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1690,14 +1732,26 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-emiratesislamic.ae/en/news-a…</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1707,27 +1761,23 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T12:44:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1736,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1745,12 +1795,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1776,14 +1826,20 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-emiratesislamic.ae/ar/news-a…</t>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp; conditions apply.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-&lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1793,27 +1849,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:43 AM UTC</t>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-23T09:43:00Z</t>
+          <t>2026-04-24T11:02:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/April/emirates-islamic-first-quarter-financial-results-2026']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1822,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -1831,12 +1887,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047193755975917822</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1862,14 +1918,16 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1879,27 +1937,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-23T06:00:00Z</t>
+          <t>2026-04-24T11:02:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1908,7 +1962,1809 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>53</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2047632125583605871</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2047631643926483032</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2047631643901390924</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2047631640168374617</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2047631639946093018</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2047556140511162463</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-24T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2047556140431556611</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-24T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2047541045768962304</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+#فخورين_بالإمارات</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2047717990762782723</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+emiratesislamic.ae/en/offers…
+#EmiratesIslamic #FrontlineHeroes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-24T16:43:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2047717920193622257</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+emiratesislamic.ae/ar/offers…
+#الإمارات_الإسلامي #أبطال_الوطن</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-24T16:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2047657974936604881</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Terms &amp; condition apply.
+To know more, please visit emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2047657972390560162</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp; discounts
+Start them young!</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young!</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2047632173461561410</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp; conditions apply.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2047632125583605871</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:01:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2047631643926483032</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2047631643901390924</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;Cs apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-24T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2047541045768962304</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-24T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,916 +2857,6 @@
         <v>207</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2047717990762782723</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-04-24T16:43:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2047717920193622257</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-04-24T16:42:00Z</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2047657974936604881</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2047657962978558100</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:02:00Z</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>iDenville</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DenvilleCommunity</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['stelpetla', 'JDunlap1974']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 12:29 AM UTC</t>
+          <t>Apr 25, 2026 · 8:54 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-25T00:29:00Z</t>
+          <t>2026-04-25T20:54:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -625,12 +625,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -656,22 +656,26 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -681,25 +685,21 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -719,12 +719,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047631640168374617</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -750,18 +750,16 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -771,17 +769,17 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -793,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -805,47 +803,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047575014564921667</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on abc-gcc.net/News/1/395058
-#ABCNews #Profit #Banking #FinancialInstitution</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -855,27 +853,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 7:15 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-24T07:15:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -893,90 +891,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047556140431556611</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Apr 25</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-24T06:00:00Z</t>
+          <t>2026-04-25T00:29:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>37</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
@@ -985,12 +975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1016,22 +1006,26 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1041,25 +1035,21 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1070,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -1079,12 +1069,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047717988195852322</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1110,18 +1100,24 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1131,32 +1127,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047717920193622257</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1196,24 +1192,18 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1223,23 +1213,23 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1252,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>212</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -1261,12 +1251,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047717917324710124</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1292,16 +1282,16 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1311,17 +1301,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1333,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1335,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047657988064727443</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1376,26 +1366,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1405,23 +1387,27 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1430,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1439,12 +1425,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047657974936604881</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
+          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1470,14 +1456,16 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1487,27 +1475,23 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1516,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1525,12 +1509,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047657972390560162</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1556,24 +1540,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1583,23 +1561,27 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -1617,12 +1599,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047657962978558100</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1648,12 +1630,16 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1663,23 +1649,23 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1692,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1701,12 +1687,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047657960227176876</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1732,26 +1718,18 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1761,21 +1739,25 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
@@ -1786,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1795,12 +1777,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047632173461561410</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1826,20 +1808,16 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt;)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1849,36 +1827,36 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-24T11:02:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -1887,12 +1865,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047632164863250935</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1918,16 +1896,12 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1937,23 +1911,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-24T11:02:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1962,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -1971,12 +1945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047632125583605871</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
+          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2002,22 +1976,12 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2027,27 +1991,23 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-24T11:01:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2056,805 +2016,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-04-24T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2047556140431556611</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-04-24T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>207</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2048386621989335442</t>
+          <t>2048386618873024952</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -571,6 +571,360 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-04-26T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+emiratesislamic.ae/en/priori…</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2048341323271336150</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2048386621989335442</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -582,7 +936,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -594,81 +948,81 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-04-26T13:00:00Z</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>2048386618873024952</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>💳 بدون رسوم سنوية
 🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
@@ -679,7 +1033,7 @@
 Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>💳 بدون رسوم سنوية
 🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
@@ -690,294 +1044,1344 @@
 Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-04-26T13:00:00Z</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>53</v>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>54</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386615450435972</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-26T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>2048341326358253773</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
 emiratesislamic.ae/en/priori…</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
 &lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-04-26T10:00:00Z</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>2048341323271336150</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
         </is>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-04-26T10:00:00Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>2048341320448495999</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
 emiratesislamic.ae/ar/priori…</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_المميزة"&gt;#الخدمات_المصرفية_المميزة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_في_الإمارات"&gt;#الخدمات_المصرفية_في_الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt;
 &lt;a href="https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/ar/priori…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_المميزة', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_في_الإمارات', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341316237426944</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2048326216122335689</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=esavings"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 9:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-26T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=esavings']</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2048311115751342110</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-26T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2048311115730288881</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115730288881</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-04-26T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-04-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2048280917030867217</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917030867217</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2048386621989335442</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.
+Apply now
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.
+Apply now
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-26T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-04-26T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+emiratesislamic.ae/en/priori…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>16h</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2026-04-26T10:00:00Z</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2048341323271336150</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2048341320448495999</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
+emiratesislamic.ae/ar/priori…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_المميزة"&gt;#الخدمات_المصرفية_المميزة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_في_الإمارات"&gt;#الخدمات_المصرفية_في_الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/ar/priori…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_المميزة', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_في_الإمارات', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
         <v>10</v>
       </c>
     </row>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,55 +541,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2048386618873024952</t>
+          <t>2048954465978339486</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+          <t>https://x.com/gold_hadas/status/2048954465978339486</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals tradingview.com/news/reuters…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/"&gt;tradingview.com/news/reuters…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -599,27 +587,27 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 28, 2026 · 2:36 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-28T02:36:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+          <t>['https://www.tradingview.com/news/reuters.com,2026-04-27:newsml_Zaw2WZ0pH:0-zawya-emirates-islamic-becomes-first-islamic-bank-in-the-uae-to-offer-digital-investment-in-precious-metals/']</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -628,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -637,45 +625,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2048341326358253773</t>
+          <t>2048953588357963815</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+          <t>https://x.com/gold_hadas/status/2048953588357963815</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+          <t>UAE’s Emirates Islamic Unveils Mobile App Platform for Secure Sharia-Compliant Gold and Silver Trading &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -685,23 +671,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-28T02:32:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-launches-sharia-compliant-digital-gold-and-silver-investment-1.500521234']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -714,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -723,43 +709,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2048341323271336150</t>
+          <t>2048928610338144280</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+          <t>https://x.com/gold_hadas/status/2048928610338144280</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals mediaoffice.ae/en/news/2026/…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>Emirates Islamic becomes first Islamic bank in the UAE to offer digital investment in precious metals &lt;a href="https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic"&gt;mediaoffice.ae/en/news/2026/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -769,23 +755,27 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 28, 2026 · 12:53 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-28T00:53:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://mediaoffice.ae/en/news/2026/april/27-04/emirates-islamic']</t>
+        </is>
+      </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -794,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -803,51 +793,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2048280917039276118</t>
+          <t>2048838102010019915</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+          <t>https://x.com/khaleejinsight/status/2048838102010019915</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khaleejinsight</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khaleejinsight</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khaleej Business Insight</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1900814841868394496/B-nstVph_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>You don’t need to fix everything at once.
-Focus on one big expense.
-Consistency creates real progress.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App khaleejbusinessinsight.com/e… via @khaleejbusinessinsight.com 
+Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
+#DigitalGold #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>You don’t need to fix everything at once.
-Focus on one big expense.
-Consistency creates real progress.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Emirates Islamic Launches Digital Gold Trading via Mobile App &lt;a href="https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/"&gt;khaleejbusinessinsight.com/e…&lt;/a&gt; via @khaleejbusinessinsight.com 
+Emirates Islamic introduces digital gold trading via its mobile app, making precious metal investing more accessible and flexible.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DigitalGold"&gt;#DigitalGold&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -857,23 +843,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 6:54 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-26T06:00:00Z</t>
+          <t>2026-04-27T18:54:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://khaleejbusinessinsight.com/emirates-islamic-launches-digital-gold-trading-via-mobile-app/', 'https://x.com/search?f=tweets&amp;q=%23DigitalGold', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -886,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -895,57 +881,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2048386621989335442</t>
+          <t>2048792635020612079</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+          <t>https://x.com/gold_hadas/status/2048792635020612079</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp; lifestyle benefits
-And much more.
-Terms &amp; conditions apply.
-Apply now
-emiratesislamic.ae/en/person…</t>
+          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals menafn.com/1111036523/Emirat…</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp;amp; lifestyle benefits
-And much more.
-Terms &amp;amp; conditions apply.
-Apply now
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Emirates Islamic Becomes First Islamic Bank In The UAE To Offer Digital Investment In Precious Metals &lt;a href="https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals"&gt;menafn.com/1111036523/Emirat…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -955,36 +927,36 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 27, 2026 · 3:53 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-27T15:53:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+          <t>['https://menafn.com/1111036523/Emirates-Islamic-Becomes-First-Islamic-Bank-In-The-UAE-To-Offer-Digital-Investment-In-Precious-Metals']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -993,55 +965,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2048386618873024952</t>
+          <t>2048773845776310425</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+          <t>https://x.com/GCCBusinessNews/status/2048773845776310425</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/GCCBusinessNews</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>GCCBusinessNews</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>GCC Business News</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Emirates Islamic to offer digital investment in precious metals
+gccbusinessnews.com/emirates…
+#EmiratesIslamic #GoldInvestment #SilverInvestment #ShariahCompliant #DigitalBanking #PreciousMetals #WealthManagement #GCCBusinessNews @emiratesislamic</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Emirates Islamic to offer digital investment in precious metals
+&lt;a href="https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/"&gt;gccbusinessnews.com/emirates…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GoldInvestment"&gt;#GoldInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SilverInvestment"&gt;#SilverInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ShariahCompliant"&gt;#ShariahCompliant&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1051,27 +1015,27 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 27, 2026 · 2:38 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-27T14:38:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+          <t>['https://www.gccbusinessnews.com/emirates-islamic-offers-digital-investment/', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23GoldInvestment', 'https://x.com/search?f=tweets&amp;q=%23SilverInvestment', 'https://x.com/search?f=tweets&amp;q=%23ShariahCompliant', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1080,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1089,77 +1053,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2048386615450435972</t>
+          <t>2048747126566641772</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386615450435972</t>
+          <t>https://x.com/gentle_arch/status/2048747126566641772</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gentle_arch</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gentle_arch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mo FiraaS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1867089865558347776/lkpOodzk_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+          <t>يعني نشتري وسبيكة تصل عندهم ولا في توصيل؟؟؟</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 27, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-27T12:52:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1168,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1177,73 +1137,71 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2048341326358253773</t>
+          <t>2048724846792855697</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
+          <t>Number dm’ed as requested</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+          <t>Number dm’ed as requested</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 11:24 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T11:24:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1254,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1263,43 +1221,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2048341323271336150</t>
+          <t>2048711386818084907</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+          <t>https://x.com/Ldyheart/status/2048711386818084907</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Ldyheart</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ldyheart</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>RV Global Reset</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016603167585087489/50LxYE_N_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service &lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1314,18 +1272,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 10:30 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T10:30:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1334,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1343,45 +1305,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2048341320448495999</t>
+          <t>2048699606029234189</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
+          <t>https://x.com/khaleejtimes/status/2048699606029234189</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khaleejtimes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khaleejtimes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khaleej Times</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1662009811242831874/ZUTWSfk4_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
-emiratesislamic.ae/ar/priori…</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE's first digital investment service
+khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_المميزة"&gt;#الخدمات_المصرفية_المميزة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_في_الإمارات"&gt;#الخدمات_المصرفية_في_الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/ar/priori…&lt;/a&gt;</t>
+          <t>Buy, sell gold online: Emirates Islamic launches UAE&amp;#39;s first digital investment service
+&lt;a href="https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1391,36 +1353,36 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T09:43:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_المميزة', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_في_الإمارات', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+          <t>['https://www.khaleejtimes.com/business/emirates-islamic-uae-first-digital-gold-investment-service']</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="12">
@@ -1429,69 +1391,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2048341316237426944</t>
+          <t>2048694049578574033</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341316237426944</t>
+          <t>https://x.com/khalifaa_rashed/status/2048694049578574033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/khalifaa_rashed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khalifaa_rashed</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Khalef Saad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1902376067718848512/dbP8oWQE_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+          <t>استثمار رقمي فـ الذهب والفضة بطريقة آمنة ومتوافقة مع الشريعة يعطي ثقة أكبر للمتعاملين</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T09:21:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1500,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1509,54 +1475,54 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2048326216122335689</t>
+          <t>2048690739530412259</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+          <t>https://x.com/bde__ir/status/2048690739530412259</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/bde__ir</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>bde__ir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>بدر ال مشاري.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1866799615325929472/IQ77nzLh_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
-تفضل بزيارة
-emiratesislamic.ae/ar/offers…</t>
+          <t>"الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من 'الإمارات الإسلامي' تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
-تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=esavings"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>&amp;#34;الذهب والفضة.. بين يديك بضغطة زر! خطوة ذكية من &amp;#39;الإمارات الإسلامي&amp;#39; تدمج بين الأمان الشرعي والحلول الرقمية السهلة. الآن أصبح الاستثمار في المعادن الثمينة متاحاً للجميع بسلاسة وموثوقية عالية عبر التطبيق. 📱⚖️ابتكار يعزز مكانة الصيرفة الإسلامية كقائد للتحول الرقمي في المنطقة. 🚀🇦🇪</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['DXBMediaOffice', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>18h</t>
@@ -1564,20 +1530,16 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 9:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:08 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-26T09:00:00Z</t>
+          <t>2026-04-27T09:08:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=esavings']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -1588,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>56</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -1597,45 +1559,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2048311115751342110</t>
+          <t>2048689865970348293</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+          <t>https://x.com/DXBMediaOffice/status/2048689865970348293</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/DXBMediaOffice</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DXBMediaOffice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Dubai Media Office</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526475569885548546/wQzde3FB_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering, a first-of-its-kind by an Islamic bank in the UAE, empowers customers to buy and sell certified physical gold and silver bars in a secure environment, providing a convenient way to diversify their portfolios and preserve investment value.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1645,17 +1605,17 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+          <t>Apr 27, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-26T08:00:00Z</t>
+          <t>2026-04-27T09:05:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -1664,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>92</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="15">
@@ -1679,45 +1639,51 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2048311115730288881</t>
+          <t>2048687555772666020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048311115730288881</t>
+          <t>https://x.com/FintechGate1/status/2048687555772666020</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
+fintechgate.net/sa1g | التفاصيل 
+@emiratesislamic
+#fintech_gate
+#الإمارات_الإسلامي #الإمارات_العربية_المتحدة #حلول_رقمية_للاستثمار  #المعادن_الثمينة</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>«الإمارات الإسلامي» أول مصرف إسلامي في دولة الإمارات العربية المتحدة يطلق حلول رقمية للاستثمار في المعادن الثمينة
+&lt;a href="https://fintechgate.net/sa1g"&gt;fintechgate.net/sa1g&lt;/a&gt; | التفاصيل 
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_العربية_المتحدة"&gt;#الإمارات_العربية_المتحدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23حلول_رقمية_للاستثمار"&gt;#حلول_رقمية_للاستثمار&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23المعادن_الثمينة"&gt;#المعادن_الثمينة&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1732,16 +1698,20 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:55 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-26T08:00:00Z</t>
+          <t>2026-04-27T08:55:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://fintechgate.net/sa1g', 'https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_العربية_المتحدة', 'https://x.com/search?f=tweets&amp;q=%23حلول_رقمية_للاستثمار', 'https://x.com/search?f=tweets&amp;q=%23المعادن_الثمينة']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -1752,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1761,51 +1731,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2048280917039276118</t>
+          <t>2048679648536752433</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+          <t>https://x.com/NazzysCt/status/2048679648536752433</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>You don’t need to fix everything at once.
-Focus on one big expense.
-Consistency creates real progress.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>@emiratesislamic I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
+Thank you.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>You don’t need to fix everything at once.
-Focus on one big expense.
-Consistency creates real progress.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I would truly appreciate it if you could make an exception and reconsider reversing this charge as a gesture of goodwill. Your support during this time would mean a lot.
+Thank you.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1815,27 +1779,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-26T06:00:00Z</t>
+          <t>2026-04-27T08:24:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1844,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1853,51 +1817,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2048280917030867217</t>
+          <t>2048679565225324653</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048280917030867217</t>
+          <t>https://x.com/NazzysCt/status/2048679565225324653</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
-ابدأ بمصروف رئيسي واحد.
-الاستمرارية تصنع تقدّماً حقيقياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
+@emiratesislamic</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
-ابدأ بمصروف رئيسي واحد.
-الاستمرارية تصنع تقدّماً حقيقياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>I fully understand the policy, however I’m currently facing financial difficulties due to ongoing war-related impacts affecting my payouts. I’ve been a loyal customer for over 10 years and have always maintained my relationship in good faith.
+&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1907,27 +1865,27 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-26T06:00:00Z</t>
+          <t>2026-04-27T08:24:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1936,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1945,57 +1903,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2048386621989335442</t>
+          <t>2048679400204644634</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+          <t>https://x.com/NazzysCt/status/2048679400204644634</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/NazzysCt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>NazzysCt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Janyt - 10XV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp; lifestyle benefits
-And much more.
-Terms &amp; conditions apply.
-Apply now
-emiratesislamic.ae/en/person…</t>
+          <t>Dear @EmiratesIslamic,
+I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>✨ Up to 6% back, unlimited
-🎁 Up to AED 750 welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp;amp; lifestyle benefits
-And much more.
-Terms &amp;amp; conditions apply.
-Apply now
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Dear &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt;,
+I kindly request your support in waiving the over-limit charge applied to my card. I contacted customer service, but was informed that a waiver can only be requested once per year since my last request was in July.</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2005,36 +1951,36 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 27, 2026 · 8:23 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-27T08:23:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2043,12 +1989,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2048386618873024952</t>
+          <t>2048643306221957276</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2074,24 +2020,20 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2101,23 +2043,23 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-26T13:00:00Z</t>
+          <t>2026-04-27T06:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2127,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -2139,45 +2081,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2048341326358253773</t>
+          <t>2048641511525585317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Allapichai25998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Allapichai25998</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sahul Allapichai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
+          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2187,27 +2127,27 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 5:52 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T05:52:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2216,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2225,12 +2165,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2048341323271336150</t>
+          <t>2048854699953021336</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+          <t>https://x.com/emiratesislamic/status/2048854699953021336</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2256,12 +2196,18 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
+نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>إنفاقك الأكبر ليس دائماً كما تعتقد.
+نصيحة: قسّم مصروفاتك الأسبوع الماضي إلى فئات، وقد تتفاجأ بما يتصدر القائمة.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2271,23 +2217,27 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 8:00 PM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T20:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2296,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -2305,12 +2255,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2048341320448495999</t>
+          <t>2048770536407232972</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
+          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2336,14 +2286,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
-emiratesislamic.ae/ar/priori…</t>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_المميزة"&gt;#الخدمات_المصرفية_المميزة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_في_الإمارات"&gt;#الخدمات_المصرفية_في_الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/ar/priori…&lt;/a&gt;</t>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2353,36 +2303,2468 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-26T10:00:00Z</t>
+          <t>2026-04-27T14:25:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_المميزة', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_في_الإمارات', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
         </is>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2048770534553301143</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2048770531961327711</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2048770529725681780</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770529725681780</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Emirates Islamic’s API Banking helps businesses optimise operations with seamless integration, real-time control, and smarter cash management, all within their existing systems.</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2048717801733476487</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717801733476487</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>We appreciate your contact. To assist you effectively by phone, we kindly request that you provide your registered mobile number.</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2048717683068146026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717683068146026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2048717639627751785</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717639627751785</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2048717608422187229</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048717608422187229</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['NazzysCt']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2048716097206079817</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048716097206079817</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['Allapichai25998']</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:49:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2048703707424940064</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2048703707408175195</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2048703704107205039</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703704107205039</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2048703703754932480</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703703754932480</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2048652591291093449</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2048652578930507953</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652578930507953</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp; education spends</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Apply for a Switch Cashback Credit Card and earn amazing rewards as you go:
+👍Get AED 500 guaranteed welcome bonus*
+💸On everyday spends: 8% cashback on fuel, and 4% on supermarkets, dining &amp;amp; education spends</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2048652535938887711</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2048652524018651430</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652524018651430</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>تقدم بطلب الحصول على بطاقة الاسترداد النقدي سويتش الائتمانية واستمتع بالمكافآت أينما كنت:
+👍 احصل على مكافأة ترحيبية مضمونة بقيمة 500 درهم
+💸 الإنفاق اليومي: استرداد نقدي %8 على نفقات الوقود و %4 على نفقات السوبر ماركت والمطاعم والتعليم</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2048643306221957276</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048643306221957276</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Airlines, courier services, and RTA all have official apps - use them directly.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2048643305903202426</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048643305903202426</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>شركات الطيران وخدمات التوصيل وهيئة الطرق والمواصلات لديها تطبيقات رسمية. استخدمها مباشرة وتجنب الروابط المشبوهة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2048630676312768835</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048630676312768835</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>['TariqAziz717052']</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 5:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-04-27T05:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2048770536407232972</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770536407232972</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+#الإمارات_الإسلامي #الخدمات_المصرفية_للأعمال #الحلول_الرقمية.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>وقد أكدت أحدث دراساتنا أن الشركات العالمية قادرة على تجاوز التحديات المالية التي تواجهها، والحصول على رؤية شاملة تُمكّنها من تنفيذ عمليات أسرع وأكثر أمانًا.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_للأعمال"&gt;#الخدمات_المصرفية_للأعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الحلول_الرقمية"&gt;#الحلول_الرقمية&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_للأعمال', 'https://x.com/search?f=tweets&amp;q=%23الحلول_الرقمية']</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2048770534553301143</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770534553301143</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها" الإمارات الإسلامي"، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>تُساعد واجهة برمجة التطبيقات للخدمات المصرفية، التي يقدمها&amp;#34; الإمارات الإسلامي&amp;#34;، الشركات على تعزيز عملياتها من خلال تكامل سلس، وتحكم فوري، وإدارة ذكية للنقد عبر أنظمتها الحالية.</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2048770531961327711</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048770531961327711</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>As showcased in our latest case study, even global companies can eliminate inefficiencies and gain full financial visibility with faster, more secure operations.</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-04-27T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2048724846792855697</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2048724846792855697</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NazzysCt</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Janyt - 10XV</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1694266444391890944/i1M5goYr_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Number dm’ed as requested</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Number dm’ed as requested</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 11:24 AM UTC</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-04-27T11:24:00Z</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2048703707424940064</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707424940064</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2048703707408175195</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048703707408175195</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-04-27T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2048652591291093449</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652591291093449</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>✈️On travel spends: 4% cashback on flight bookings, hotel stays &amp;amp; Dining
+💳1% cashback on other spends
+And much more.
+*Offer valid till 30 June 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2048652535938887711</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048652535938887711</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>✈️عند السفر: استرداد نقدي %4 على حجوزات الطيران والفنادق والمطاعم
+💳 استرداد نقدي %1 على النفقات المحلية والدولية الأخرى
+وغير ذلك الكثير
+* يسري العرض لغاية 30  يونيو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_switch"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 6:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-04-27T06:36:00Z</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/switch-cashback-credit-card-welcome-bonus?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_switch']</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2048641511525585317</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/Allapichai25998/status/2048641511525585317</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/Allapichai25998</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Allapichai25998</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sahul Allapichai</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Kindly deliver  the credit card or cancel the credit card. I have shared my details via direct message.</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 5:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-04-27T05:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,71 +541,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2056058327059349944</t>
+          <t>2056363681957523809</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/zlxxmz/status/2056058327059349944</t>
+          <t>https://x.com/deegrose/status/2056363681957523809</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/zlxxmz</t>
+          <t>https://x.com/deegrose</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>zlxxmz</t>
+          <t>deegrose</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>silver enthusiast #silvertwt</t>
+          <t>DeeG (Maria)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2055274316221292544/HuekIYvM_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SILVWR</t>
+          <t>Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SILVWR</t>
+          <t>Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic &lt;a href="https://www.zawya.com/en/capital-markets/loans/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-o2gyofj2"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 5:04 PM UTC</t>
+          <t>May 18, 2026 · 1:18 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-17T17:04:00Z</t>
+          <t>2026-05-18T13:18:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://www.zawya.com/en/capital-markets/loans/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-o2gyofj2']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -625,71 +625,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2055942016253444497</t>
+          <t>2056363624822694237</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/WealthCodeTruth/status/2055942016253444497</t>
+          <t>https://x.com/deegrose/status/2056363624822694237</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/WealthCodeTruth</t>
+          <t>https://x.com/deegrose</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WealthCodeTruth</t>
+          <t>deegrose</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wealth Code Truths</t>
+          <t>DeeG (Maria)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037292169132703744/g9FA9Y9t_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>This is the part they don't teach in school — and it costs most people years to figure out.</t>
+          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic zawya.com/en/multimedia/vide…</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>This is the part they don&amp;#39;t teach in school — and it costs most people years to figure out.</t>
+          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic &lt;a href="https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i"&gt;zawya.com/en/multimedia/vide…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 9:22 AM UTC</t>
+          <t>May 18, 2026 · 1:17 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-17T09:22:00Z</t>
+          <t>2026-05-18T13:17:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -709,12 +709,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2055877982883918328</t>
+          <t>2056344052182692285</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055877982883918328</t>
+          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -740,16 +740,22 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp; Conditions apply. 
+Know more
+emiratesislamic.ae/en/accoun…
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp;amp; Conditions apply. 
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -759,27 +765,27 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 5:08 AM UTC</t>
+          <t>May 18, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-17T05:08:00Z</t>
+          <t>2026-05-18T12:00:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -788,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -797,12 +803,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2055936366563787204</t>
+          <t>2056258744212730259</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055936366563787204</t>
+          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,16 +834,18 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>From bill payments to card controls, money transfers account updates and more, your banking is now simpler than ever. Access 200+ services instantly via the EI + Mobile Banking App.
-Know more:
-emiratesislamic.ae/en/person…</t>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>From bill payments to card controls, money transfers account updates and more, your banking is now simpler than ever. Access 200+ services instantly via the EI + Mobile Banking App.
-Know more:
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=eiplus"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -847,27 +855,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 9:00 AM UTC</t>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-17T09:00:00Z</t>
+          <t>2026-05-18T06:21:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=eiplus']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -876,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -885,12 +893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2055936362482737177</t>
+          <t>2056258742283329716</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055936362482737177</t>
+          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -916,16 +924,12 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>من تسديد عدة فواتير إلى التحكم في البطاقات أو التحويلات المالية أو تحديث بيانات الحساب، أصبح بإمكانك الآن الوصول إلى أكثر من 200 خدمة فوراً عبر تطبيقEI+  لخدمات المصرفية عبر الهاتف المتحرك. للمزيد، زر.
-لمعرفة المزيد، تفضل بزيارة:
-emiratesislamic.ae/ar/person…</t>
+          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>من تسديد عدة فواتير إلى التحكم في البطاقات أو التحويلات المالية أو تحديث بيانات الحساب، أصبح بإمكانك الآن الوصول إلى أكثر من 200 خدمة فوراً عبر تطبيقEI+  لخدمات المصرفية عبر الهاتف المتحرك. للمزيد، زر.
-لمعرفة المزيد، تفضل بزيارة:
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=eiplus"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -935,25 +939,21 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 9:00 AM UTC</t>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-17T09:00:00Z</t>
+          <t>2026-05-18T06:21:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=eiplus']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>1</v>
       </c>
@@ -961,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -973,12 +973,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2055877982883918328</t>
+          <t>2056258736428130347</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055877982883918328</t>
+          <t>https://x.com/emiratesislamic/status/2056258736428130347</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1004,16 +1004,12 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على "تحقق من حسابك"، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على &amp;#34;تحقق من حسابك&amp;#34;، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1023,25 +1019,21 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 5:08 AM UTC</t>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-17T05:08:00Z</t>
+          <t>2026-05-18T06:21:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>1</v>
       </c>
@@ -1049,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>56</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -1061,47 +1053,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2055877978849005786</t>
+          <t>2056242871347347594</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055877978849005786</t>
+          <t>https://x.com/Zawya/status/2056242871347347594</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Zawya</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Zawya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Zawya</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1717138378209030144/CNQxrrRP_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30 ثانية من الوعي المالي 
-في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
-#أسبوع_المال_العالمي #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
+          <t>#WATCH: The UAE retail group #BrandsForLess (BFL) has secured a 250 million dirhams ($68 million) sustainability-linked #financing facility from Emirates Islamic lseg.group/4ulht86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30 ثانية من الوعي المالي 
-في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23أسبوع_المال_العالمي"&gt;#أسبوع_المال_العالمي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23WATCH"&gt;#WATCH&lt;/a&gt;: The UAE retail group &lt;a href="/search?f=tweets&amp;amp;q=%23BrandsForLess"&gt;#BrandsForLess&lt;/a&gt; (BFL) has secured a 250 million dirhams ($68 million) sustainability-linked &lt;a href="/search?f=tweets&amp;amp;q=%23financing"&gt;#financing&lt;/a&gt; facility from Emirates Islamic &lt;a href="https://lseg.group/4ulht86"&gt;lseg.group/4ulht86&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1116,31 +1104,31 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 5:08 AM UTC</t>
+          <t>May 18, 2026 · 5:17 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-17T05:08:00Z</t>
+          <t>2026-05-18T05:17:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23أسبوع_المال_العالمي', 'https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23WATCH', 'https://x.com/search?f=tweets&amp;q=%23BrandsForLess', 'https://x.com/search?f=tweets&amp;q=%23financing', 'https://lseg.group/4ulht86']</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
@@ -1149,71 +1137,75 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2056058327059349944</t>
+          <t>2056241126827241821</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/zlxxmz/status/2056058327059349944</t>
+          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/zlxxmz</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>zlxxmz</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>silver enthusiast #silvertwt</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2055274316221292544/HuekIYvM_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SILVWR</t>
+          <t>30 Seconds of Financial Awareness 
+This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
+#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SILVWR</t>
+          <t>30 Seconds of Financial Awareness 
+This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
+&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 5:04 PM UTC</t>
+          <t>May 18, 2026 · 5:11 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-17T17:04:00Z</t>
+          <t>2026-05-18T05:11:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1224,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -1233,71 +1225,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2055942016253444497</t>
+          <t>2056359157968585025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/WealthCodeTruth/status/2055942016253444497</t>
+          <t>https://x.com/emiratesislamic/status/2056359157968585025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/WealthCodeTruth</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WealthCodeTruth</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wealth Code Truths</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037292169132703744/g9FA9Y9t_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>This is the part they don't teach in school — and it costs most people years to figure out.</t>
+          <t>Keep your money in the right hands 🤝
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>This is the part they don&amp;#39;t teach in school — and it costs most people years to figure out.</t>
+          <t>Keep your money in the right hands 🤝
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 9:22 AM UTC</t>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-17T09:22:00Z</t>
+          <t>2026-05-18T13:00:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1308,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -1317,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2055936366563787204</t>
+          <t>2056359156047577367</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055936366563787204</t>
+          <t>https://x.com/emiratesislamic/status/2056359156047577367</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1348,16 +1342,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>From bill payments to card controls, money transfers account updates and more, your banking is now simpler than ever. Access 200+ services instantly via the EI + Mobile Banking App.
-Know more:
-emiratesislamic.ae/en/person…</t>
+          <t>Sending money home today? 💸🌍
+Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or "helpers" on social media offering better rates, they're often looking for your login credentials.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>From bill payments to card controls, money transfers account updates and more, your banking is now simpler than ever. Access 200+ services instantly via the EI + Mobile Banking App.
-Know more:
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=eiplus"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Sending money home today? 💸🌍
+Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or &amp;#34;helpers&amp;#34; on social media offering better rates, they&amp;#39;re often looking for your login credentials.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1367,25 +1359,21 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 17, 2026 · 9:00 AM UTC</t>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-17T09:00:00Z</t>
+          <t>2026-05-18T13:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/ei-plus-mobile-banking-app?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=eiplus']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>1</v>
       </c>
@@ -1396,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -1405,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2055877982883918328</t>
+          <t>2056359152201384153</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2055877982883918328</t>
+          <t>https://x.com/emiratesislamic/status/2056359152201384153</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1435,56 +1423,2044 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
+فأموالك تستحق وجهة موثوقة.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
+فأموالك تستحق وجهة موثوقة.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-05-18T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2056359147562504457</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056359147562504457</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>هل ترغب بإرسال الأموال إلى عائلتك اليوم؟ 💸🌍
+لتحويلات عبر خدمة QuickRemit الآمنة والموثوقة، استخدم تطبيق + EI للخدمات المصرفية عبر الهاتف المحمول فقط. لا تنخدع بالروابط الخارجية أو الحسابات التي تَعِدك بأسعار تحويل استثنائية عبر مواقع التواصل الاجتماعي،</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>هل ترغب بإرسال الأموال إلى عائلتك اليوم؟ 💸🌍
+لتحويلات عبر خدمة QuickRemit الآمنة والموثوقة، استخدم تطبيق + EI للخدمات المصرفية عبر الهاتف المحمول فقط. لا تنخدع بالروابط الخارجية أو الحسابات التي تَعِدك بأسعار تحويل استثنائية عبر مواقع التواصل الاجتماعي،</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-05-18T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2056344052182692285</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp; Conditions apply. 
+Know more
+emiratesislamic.ae/en/accoun…
+#EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp;amp; Conditions apply. 
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 12:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2056344048902762537</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056344048902762537</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>وديعة الوكالة بالاستثمار ذات العوائد المضاعفة
+دع ودائعك تنمو وتكبر مع معدلات الأرباح المميزة وتوزيع الأرباح الدوري.
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة 
+emiratesislamic.ae/ar/accoun…
+#الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>وديعة الوكالة بالاستثمار ذات العوائد المضاعفة
+دع ودائعك تنمو وتكبر مع معدلات الأرباح المميزة وتوزيع الأرباح الدوري.
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة 
+&lt;a href="https://www.emiratesislamic.ae/ar/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/ar/accoun…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 12:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2056312855901692349</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056312855901692349</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['rami_shehada']</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2056312760145682889</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056312760145682889</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['rami_shehada']</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2056312704801841358</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056312704801841358</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['rami_shehada']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2056312626104119775</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056312626104119775</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['rami_shehada']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:55:00Z</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2056307273295642795</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056307273295642795</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['salem_UAE_S']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:33 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:33:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2056307107352219838</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056307107352219838</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['salem_UAE_S']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 9:33 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:33:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2056258744212730259</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2056258742283329716</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2056258740056150094</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258740056150094</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
+لا تقع في الفخ. احذر الاحتيال #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+#الإمارات_الإسلامي_ضد_الاحتيال</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
+لا تقع في الفخ. احذر الاحتيال &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال"&gt;#الإمارات_الإسلامي_ضد_الاحتيال&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2056258736428130347</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258736428130347</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على "تحقق من حسابك"، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على &amp;#34;تحقق من حسابك&amp;#34;، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2056241126827241821</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>30 Seconds of Financial Awareness 
 This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
 #GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>30 Seconds of Financial Awareness 
 This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
 &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>May 17, 2026 · 5:08 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-05-17T05:08:00Z</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 5:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-05-18T05:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2056241121672515723</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056241121672515723</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30 ثانية من الوعي المالي 
+في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
+#أسبوع_المال_العالمي #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>30 ثانية من الوعي المالي 
+في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
+&lt;a href="/search?f=tweets&amp;amp;q=%23أسبوع_المال_العالمي"&gt;#أسبوع_المال_العالمي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 5:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-05-18T05:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23أسبوع_المال_العالمي', 'https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>56</v>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2056359157968585025</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056359157968585025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Keep your money in the right hands 🤝
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Keep your money in the right hands 🤝
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-05-18T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2056359156047577367</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056359156047577367</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sending money home today? 💸🌍
+Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or "helpers" on social media offering better rates, they're often looking for your login credentials.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sending money home today? 💸🌍
+Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or &amp;#34;helpers&amp;#34; on social media offering better rates, they&amp;#39;re often looking for your login credentials.</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-05-18T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2056359152201384153</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056359152201384153</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
+فأموالك تستحق وجهة موثوقة.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
+فأموالك تستحق وجهة موثوقة.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-05-18T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2056344052182692285</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp; Conditions apply. 
+Know more
+emiratesislamic.ae/en/accoun…
+#EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Booster Wakala Deposit
+Grow your deposits with attractive profit rates and periodic profit payout.
+Terms &amp;amp; Conditions apply. 
+Know more
+&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 12:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2056258744212730259</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2056258742283329716</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2056258740056150094</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056258740056150094</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
+لا تقع في الفخ. احذر الاحتيال #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+#الإمارات_الإسلامي_ضد_الاحتيال</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
+لا تقع في الفخ. احذر الاحتيال &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال"&gt;#الإمارات_الإسلامي_ضد_الاحتيال&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 6:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-05-18T06:21:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2056241126827241821</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30 Seconds of Financial Awareness 
+This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
+#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30 Seconds of Financial Awareness 
+This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
+&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>May 18, 2026 · 5:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-05-18T05:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/EI_tweet.xlsx
+++ b/EI_tweet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2056363681957523809</t>
+          <t>2056723953301754366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2056363681957523809</t>
+          <t>https://x.com/deegrose/status/2056723953301754366</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -572,12 +572,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic zawya.com/en/capital-markets…</t>
+          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic zawya.com/en/multimedia/vide…</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic &lt;a href="https://www.zawya.com/en/capital-markets/loans/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-o2gyofj2"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
+          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic &lt;a href="https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i"&gt;zawya.com/en/multimedia/vide…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -592,18 +592,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:18 PM UTC</t>
+          <t>May 19, 2026 · 1:09 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-18T13:18:00Z</t>
+          <t>2026-05-19T13:09:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['https://www.zawya.com/en/capital-markets/loans/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-o2gyofj2']</t>
+          <t>['https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i']</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -625,43 +625,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2056363624822694237</t>
+          <t>2056722807728242782</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2056363624822694237</t>
+          <t>https://x.com/emiratesislamic/status/2056722807728242782</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>deegrose</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DeeG (Maria)</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic zawya.com/en/multimedia/vide…</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VIDEO: Brands for Less secures $68mln ESG-linked loan facility from Emirates Islamic &lt;a href="https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i"&gt;zawya.com/en/multimedia/vide…&lt;/a&gt;</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -676,20 +678,16 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:17 PM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-18T13:17:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://www.zawya.com/en/multimedia/videos/brands-for-less-secures-68mln-esg-linked-loan-facility-from-emirates-islamic-pchu3j6i']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -700,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -709,81 +707,71 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2056344052182692285</t>
+          <t>2056676845337338096</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
+          <t>https://x.com/Mshaheen111/status/2056676845337338096</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Mshaheen111</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mshaheen111</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>iMohamed</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2031124803650990080/2TyK4gop_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp; Conditions apply. 
-Know more
-emiratesislamic.ae/en/accoun…
-#EmiratesIslamic</t>
+          <t>انزين هذا العرض موجود سابقا ولكن اللي اختلف الان اضافة عرض حصري لحماة الوطن !</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp;amp; Conditions apply. 
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>انزين هذا العرض موجود سابقا ولكن اللي اختلف الان اضافة عرض حصري لحماة الوطن !</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 12:00 PM UTC</t>
+          <t>May 19, 2026 · 10:02 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-18T12:00:00Z</t>
+          <t>2026-05-19T10:02:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -794,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -803,79 +791,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2056258744212730259</t>
+          <t>2056637756068257885</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
+          <t>https://x.com/Saeed_20212/status/2056637756068257885</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Saeed_20212</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Saeed_20212</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>سعيد UAE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
+          <t>شكر خاص للأخ  عبدالله تعامل راقي ومتابعة حل الإشكالية ✅</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+          <t>شكر خاص للأخ  عبدالله تعامل راقي ومتابعة حل الإشكالية ✅</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
+          <t>May 19, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-18T06:21:00Z</t>
+          <t>2026-05-19T07:27:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -884,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -893,12 +875,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2056258742283329716</t>
+          <t>2056623389427511647</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
+          <t>https://x.com/emiratesislamic/status/2056623389427511647</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -924,12 +906,18 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+          <t>You get a call from "Bank Support" saying your account is blocked. They ask for your OTP to "unfreeze" it. What do you do? 📞
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
+          <t>You get a call from &amp;#34;Bank Support&amp;#34; saying your account is blocked. They ask for your OTP to &amp;#34;unfreeze&amp;#34; it. What do you do? 📞
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -944,18 +932,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
+          <t>May 19, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-18T06:21:00Z</t>
+          <t>2026-05-19T06:30:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -964,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -973,12 +965,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2056258736428130347</t>
+          <t>2056722807728242782</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056258736428130347</t>
+          <t>https://x.com/emiratesislamic/status/2056722807728242782</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1004,12 +996,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على "تحقق من حسابك"، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على &amp;#34;تحقق من حسابك&amp;#34;، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1019,32 +1013,32 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-18T06:21:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>191</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -1053,43 +1047,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2056242871347347594</t>
+          <t>2056722801713693057</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/Zawya/status/2056242871347347594</t>
+          <t>https://x.com/emiratesislamic/status/2056722801713693057</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/Zawya</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zawya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zawya</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1717138378209030144/CNQxrrRP_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>#WATCH: The UAE retail group #BrandsForLess (BFL) has secured a 250 million dirhams ($68 million) sustainability-linked #financing facility from Emirates Islamic lseg.group/4ulht86</t>
+          <t>اطلب "صندوق عيدية السبائك الذهبية" الخاص بك اليوم عن طريق تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23WATCH"&gt;#WATCH&lt;/a&gt;: The UAE retail group &lt;a href="/search?f=tweets&amp;amp;q=%23BrandsForLess"&gt;#BrandsForLess&lt;/a&gt; (BFL) has secured a 250 million dirhams ($68 million) sustainability-linked &lt;a href="/search?f=tweets&amp;amp;q=%23financing"&gt;#financing&lt;/a&gt; facility from Emirates Islamic &lt;a href="https://lseg.group/4ulht86"&gt;lseg.group/4ulht86&lt;/a&gt;</t>
+          <t>اطلب &amp;#34;صندوق عيدية السبائك الذهبية&amp;#34; الخاص بك اليوم عن طريق تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1099,36 +1093,32 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 5:17 AM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-18T05:17:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23WATCH', 'https://x.com/search?f=tweets&amp;q=%23BrandsForLess', 'https://x.com/search?f=tweets&amp;q=%23financing', 'https://lseg.group/4ulht86']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -1137,12 +1127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2056241126827241821</t>
+          <t>2056722797024407698</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
+          <t>https://x.com/emiratesislamic/status/2056722797024407698</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1168,16 +1158,12 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>بمناسبة عيد الأضحى المبارك، نقدم لكم "صندوق عيدية السبائك الذهبية" من الإمارات الإسلامي. هدية راقية تجسد معنى العطاء في العيد وتخلد أجمل اللحظات. امنحوا أحبائكم عيدية تبقى قيمتها مع الزمن.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>بمناسبة عيد الأضحى المبارك، نقدم لكم &amp;#34;صندوق عيدية السبائك الذهبية&amp;#34; من الإمارات الإسلامي. هدية راقية تجسد معنى العطاء في العيد وتخلد أجمل اللحظات. امنحوا أحبائكم عيدية تبقى قيمتها مع الزمن.</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1187,36 +1173,32 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 5:11 AM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-18T05:11:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>36</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -1225,12 +1207,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2056359157968585025</t>
+          <t>2056679406286909746</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056359157968585025</t>
+          <t>https://x.com/emiratesislamic/status/2056679406286909746</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1256,42 +1238,40 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Keep your money in the right hands 🤝
-emiratesislamic.ae/en/Person…</t>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Keep your money in the right hands 🤝
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['Saeed_20212']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
+          <t>May 19, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-18T13:00:00Z</t>
+          <t>2026-05-19T10:12:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1302,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1311,12 +1291,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2056359156047577367</t>
+          <t>2056661144446652894</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056359156047577367</t>
+          <t>https://x.com/emiratesislamic/status/2056661144446652894</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1342,14 +1322,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sending money home today? 💸🌍
-Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or "helpers" on social media offering better rates, they're often looking for your login credentials.</t>
+          <t>📈 Attractive finance profit rates
+💳 Zero processing fees
+*For eligible customers only
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sending money home today? 💸🌍
-Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or &amp;#34;helpers&amp;#34; on social media offering better rates, they&amp;#39;re often looking for your login credentials.</t>
+          <t>📈 Attractive finance profit rates
+💳 Zero processing fees
+*For eligible customers only
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1359,23 +1343,23 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
+          <t>May 19, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-18T13:00:00Z</t>
+          <t>2026-05-19T09:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1384,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -1393,12 +1377,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2056359152201384153</t>
+          <t>2056661142160720059</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056359152201384153</t>
+          <t>https://x.com/emiratesislamic/status/2056661142160720059</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1424,16 +1408,16 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
-فأموالك تستحق وجهة موثوقة.
-emiratesislamic.ae/ar/Person…</t>
+          <t>For everything you do for the nation - thank you. We are proud to offer you an exclusive bundle of banking benefits including:
+💰 10% cashback up to AED 500 on Covered Cards*
+🎁 AED 100,000 to be won – 10 lucky winners get AED 10,000 AED each with Kunooz Millionaire Account</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
-فأموالك تستحق وجهة موثوقة.
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>For everything you do for the nation - thank you. We are proud to offer you an exclusive bundle of banking benefits including:
+💰 10% cashback up to AED 500 on Covered Cards*
+🎁 AED 100,000 to be won – 10 lucky winners get AED 10,000 AED each with Kunooz Millionaire Account</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1443,25 +1427,21 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
+          <t>May 19, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-18T13:00:00Z</t>
+          <t>2026-05-19T09:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>1</v>
       </c>
@@ -1472,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -1481,12 +1461,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2056359147562504457</t>
+          <t>2056661136766886380</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056359147562504457</t>
+          <t>https://x.com/emiratesislamic/status/2056661136766886380</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1512,14 +1492,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>هل ترغب بإرسال الأموال إلى عائلتك اليوم؟ 💸🌍
-لتحويلات عبر خدمة QuickRemit الآمنة والموثوقة، استخدم تطبيق + EI للخدمات المصرفية عبر الهاتف المحمول فقط. لا تنخدع بالروابط الخارجية أو الحسابات التي تَعِدك بأسعار تحويل استثنائية عبر مواقع التواصل الاجتماعي،</t>
+          <t>حصرياً لأبطال الوطن، تأجيل الأقساط الأولى للتمويل لمدة تصل إلى 4 شهور ومعدلات أرباح خاصة على التمويل وخصومات على رسوم الإجراءات وجوائز كبرى على حساب التوفير واسترداد نقدي على الانفاق من البطاقات المغطاه والمزيد.
+تطبق الشروط والأحكام.
+لمعرفة المزيد: 
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>هل ترغب بإرسال الأموال إلى عائلتك اليوم؟ 💸🌍
-لتحويلات عبر خدمة QuickRemit الآمنة والموثوقة، استخدم تطبيق + EI للخدمات المصرفية عبر الهاتف المحمول فقط. لا تنخدع بالروابط الخارجية أو الحسابات التي تَعِدك بأسعار تحويل استثنائية عبر مواقع التواصل الاجتماعي،</t>
+          <t>حصرياً لأبطال الوطن، تأجيل الأقساط الأولى للتمويل لمدة تصل إلى 4 شهور ومعدلات أرباح خاصة على التمويل وخصومات على رسوم الإجراءات وجوائز كبرى على حساب التوفير واسترداد نقدي على الانفاق من البطاقات المغطاه والمزيد.
+تطبق الشروط والأحكام.
+لمعرفة المزيد: 
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1529,32 +1513,36 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
+          <t>May 19, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-18T13:00:00Z</t>
+          <t>2026-05-19T09:00:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
       <c r="V13" t="n">
-        <v>152</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14">
@@ -1563,12 +1551,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2056344052182692285</t>
+          <t>2056623389427511647</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
+          <t>https://x.com/emiratesislamic/status/2056623389427511647</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1594,22 +1582,18 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp; Conditions apply. 
-Know more
-emiratesislamic.ae/en/accoun…
-#EmiratesIslamic</t>
+          <t>You get a call from "Bank Support" saying your account is blocked. They ask for your OTP to "unfreeze" it. What do you do? 📞
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp;amp; Conditions apply. 
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>You get a call from &amp;#34;Bank Support&amp;#34; saying your account is blocked. They ask for your OTP to &amp;#34;unfreeze&amp;#34; it. What do you do? 📞
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1619,23 +1603,23 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 12:00 PM UTC</t>
+          <t>May 19, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-18T12:00:00Z</t>
+          <t>2026-05-19T06:30:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1648,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -1657,12 +1641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2056344048902762537</t>
+          <t>2056623386067960027</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056344048902762537</t>
+          <t>https://x.com/emiratesislamic/status/2056623386067960027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1688,22 +1672,18 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>وديعة الوكالة بالاستثمار ذات العوائد المضاعفة
-دع ودائعك تنمو وتكبر مع معدلات الأرباح المميزة وتوزيع الأرباح الدوري.
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة 
-emiratesislamic.ae/ar/accoun…
-#الإمارات_الإسلامي</t>
+          <t>وصلك اتصال من "خدمة العملاء" يخبرك أن حسابك مجمد، ويطلب منك  كلمة السر لمرة واحدة لـ"إلغاء التجميد". كيف ستتصرف؟ 📞
+لا تقع في الفخ. احذر الاحتيال #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+#الإمارات_الإسلامي_ضد_الاحتيال
+#معاً_ضد_الاحتيال</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>وديعة الوكالة بالاستثمار ذات العوائد المضاعفة
-دع ودائعك تنمو وتكبر مع معدلات الأرباح المميزة وتوزيع الأرباح الدوري.
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة 
-&lt;a href="https://www.emiratesislamic.ae/ar/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/ar/accoun…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+          <t>وصلك اتصال من &amp;#34;خدمة العملاء&amp;#34; يخبرك أن حسابك مجمد، ويطلب منك  كلمة السر لمرة واحدة لـ&amp;#34;إلغاء التجميد&amp;#34;. كيف ستتصرف؟ 📞
+لا تقع في الفخ. احذر الاحتيال &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال"&gt;#الإمارات_الإسلامي_ضد_الاحتيال&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23معاً_ضد_الاحتيال"&gt;#معاً_ضد_الاحتيال&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1713,23 +1693,23 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 12:00 PM UTC</t>
+          <t>May 19, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-18T12:00:00Z</t>
+          <t>2026-05-19T06:30:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23معاً_ضد_الاحتيال']</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1742,7 +1722,7 @@
         <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>101</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -1751,12 +1731,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2056312855901692349</t>
+          <t>2056722807728242782</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056312855901692349</t>
+          <t>https://x.com/emiratesislamic/status/2056722807728242782</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1782,36 +1762,34 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Introducing the Emirates Islamic “Gold Eidiya Box”, an elegant expression of Eid gifting designed to create moments of lasting value. Gift your loved ones a timeless Eidiya. 
+Order your “Gold Eidiya Box” today via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['rami_shehada']</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:56 AM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-18T09:56:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1826,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
@@ -1835,12 +1813,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2056312760145682889</t>
+          <t>2056722801713693057</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056312760145682889</t>
+          <t>https://x.com/emiratesislamic/status/2056722801713693057</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1866,44 +1844,38 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>اطلب "صندوق عيدية السبائك الذهبية" الخاص بك اليوم عن طريق تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>اطلب &amp;#34;صندوق عيدية السبائك الذهبية&amp;#34; الخاص بك اليوم عن طريق تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['rami_shehada']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:55 AM UTC</t>
+          <t>May 19, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-18T09:55:00Z</t>
+          <t>2026-05-19T13:05:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1912,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
@@ -1921,45 +1893,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2056312704801841358</t>
+          <t>2056676845337338096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056312704801841358</t>
+          <t>https://x.com/Mshaheen111/status/2056676845337338096</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Mshaheen111</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mshaheen111</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>iMohamed</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2031124803650990080/2TyK4gop_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>انزين هذا العرض موجود سابقا ولكن اللي اختلف الان اضافة عرض حصري لحماة الوطن !</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
+          <t>انزين هذا العرض موجود سابقا ولكن اللي اختلف الان اضافة عرض حصري لحماة الوطن !</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1968,7 +1938,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>['rami_shehada']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1978,12 +1948,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:55 AM UTC</t>
+          <t>May 19, 2026 · 10:02 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-18T09:55:00Z</t>
+          <t>2026-05-19T10:02:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1998,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2007,12 +1977,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2056312626104119775</t>
+          <t>2056661144446652894</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056312626104119775</t>
+          <t>https://x.com/emiratesislamic/status/2056661144446652894</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2038,36 +2008,38 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+          <t>📈 Attractive finance profit rates
+💳 Zero processing fees
+*For eligible customers only
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
+          <t>📈 Attractive finance profit rates
+💳 Zero processing fees
+*For eligible customers only
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['rami_shehada']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:55 AM UTC</t>
+          <t>May 19, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-18T09:55:00Z</t>
+          <t>2026-05-19T09:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2082,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -2091,12 +2063,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2056307273295642795</t>
+          <t>2056661142160720059</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056307273295642795</t>
+          <t>https://x.com/emiratesislamic/status/2056661142160720059</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2122,42 +2094,42 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>For everything you do for the nation - thank you. We are proud to offer you an exclusive bundle of banking benefits including:
+💰 10% cashback up to AED 500 on Covered Cards*
+🎁 AED 100,000 to be won – 10 lucky winners get AED 10,000 AED each with Kunooz Millionaire Account</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>For everything you do for the nation - thank you. We are proud to offer you an exclusive bundle of banking benefits including:
+💰 10% cashback up to AED 500 on Covered Cards*
+🎁 AED 100,000 to be won – 10 lucky winners get AED 10,000 AED each with Kunooz Millionaire Account</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['salem_UAE_S']</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:33 AM UTC</t>
+          <t>May 19, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-18T09:33:00Z</t>
+          <t>2026-05-19T09:00:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2166,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -2175,43 +2147,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2056307107352219838</t>
+          <t>2056637756068257885</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056307107352219838</t>
+          <t>https://x.com/Saeed_20212/status/2056637756068257885</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Saeed_20212</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Saeed_20212</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>سعيد UAE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>شكر خاص للأخ  عبدالله تعامل راقي ومتابعة حل الإشكالية ✅</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>شكر خاص للأخ  عبدالله تعامل راقي ومتابعة حل الإشكالية ✅</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2220,28 +2192,28 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>['salem_UAE_S']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 9:33 AM UTC</t>
+          <t>May 19, 2026 · 7:27 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-18T09:33:00Z</t>
+          <t>2026-05-19T07:27:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2250,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -2259,12 +2231,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2056258744212730259</t>
+          <t>2056623389427511647</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
+          <t>https://x.com/emiratesislamic/status/2056623389427511647</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2290,7 +2262,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+          <t>You get a call from "Bank Support" saying your account is blocked. They ask for your OTP to "unfreeze" it. What do you do? 📞
 Do not fall for the traps. Stay alert to scams.
 #EIAgainstFraud with Emirates Islamic.
 #TogetherAgainstFraud</t>
@@ -2298,7 +2270,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
+          <t>You get a call from &amp;#34;Bank Support&amp;#34; saying your account is blocked. They ask for your OTP to &amp;#34;unfreeze&amp;#34; it. What do you do? 📞
 Do not fall for the traps. Stay alert to scams.
 &lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
 &lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
@@ -2316,12 +2288,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
+          <t>May 19, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-18T06:21:00Z</t>
+          <t>2026-05-19T06:30:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
@@ -2341,1126 +2313,6 @@
       </c>
       <c r="V22" t="n">
         <v>62</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2056258742283329716</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2056258740056150094</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258740056150094</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
-لا تقع في الفخ. احذر الاحتيال #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-#الإمارات_الإسلامي_ضد_الاحتيال</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
-لا تقع في الفخ. احذر الاحتيال &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال"&gt;#الإمارات_الإسلامي_ضد_الاحتيال&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2056258736428130347</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258736428130347</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على "تحقق من حسابك"، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>هل هذا البريد الإلكتروني فعلاً من المصرف؟ 🧐 قبل الضغط على &amp;#34;تحقق من حسابك&amp;#34;، تحقق من عنوان المرسل. إذا كان بهذه الطريقة : emirates-islamic-support123@gmail.com فهذا فخ.</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2056241126827241821</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 5:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-05-18T05:11:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2056241121672515723</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056241121672515723</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30 ثانية من الوعي المالي 
-في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
-#أسبوع_المال_العالمي #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>30 ثانية من الوعي المالي 
-في أسبوع المال العالمي، تذكّر أن أبسط العادات المالية اليوم قد تصنع فرقاً كبيراً في مستقبلك.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23أسبوع_المال_العالمي"&gt;#أسبوع_المال_العالمي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 5:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-05-18T05:11:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23أسبوع_المال_العالمي', 'https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2056359157968585025</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056359157968585025</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Keep your money in the right hands 🤝
-emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Keep your money in the right hands 🤝
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-05-18T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/quick-remit']</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2056359156047577367</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056359156047577367</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sending money home today? 💸🌍
-Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or "helpers" on social media offering better rates, they're often looking for your login credentials.</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Sending money home today? 💸🌍
-Make sure you use the official EI + Mobile Banking App for your QuickRemit transfers. Avoid third-party links or &amp;#34;helpers&amp;#34; on social media offering better rates, they&amp;#39;re often looking for your login credentials.</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-05-18T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2056359152201384153</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056359152201384153</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
-فأموالك تستحق وجهة موثوقة.
-emiratesislamic.ae/ar/Person…</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>فغالباً ما يكون هدفها الوصول إلى بياناتك المصرفية.
-فأموالك تستحق وجهة موثوقة.
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 1:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-05-18T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/quick-remit']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2056344052182692285</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056344052182692285</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp; Conditions apply. 
-Know more
-emiratesislamic.ae/en/accoun…
-#EmiratesIslamic</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Booster Wakala Deposit
-Grow your deposits with attractive profit rates and periodic profit payout.
-Terms &amp;amp; Conditions apply. 
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=booster_wakala"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 12:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/accounts/deposit-accounts/booster-wakala-deposit?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=booster_wakala', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2056258744212730259</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258744212730259</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>The Golden Rule: We will never send you an email asking for your password or card details via a link. 
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2056258742283329716</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258742283329716</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Is that email really from us? 🧐 Before you click "Verify Account," check the sender's address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Is that email really from us? 🧐 Before you click &amp;#34;Verify Account,&amp;#34; check the sender&amp;#39;s address. If it looks like emirates-islamic-support123@gmail.com - it’s a trap.</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2056258740056150094</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056258740056150094</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
-لا تقع في الفخ. احذر الاحتيال #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-#الإمارات_الإسلامي_ضد_الاحتيال</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>القاعدة الذهبية: لن نطلب منك أبداً كلمة مرورك أو بيانات بطاقتك عبر رابط في بريد إلكتروني.
-لا تقع في الفخ. احذر الاحتيال &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال"&gt;#الإمارات_الإسلامي_ضد_الاحتيال&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 6:21 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-05-18T06:21:00Z</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي_ضد_الاحتيال']</t>
-        </is>
-      </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2056241126827241821</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2056241126827241821</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-#GlobalMoneyWeek #EIFinancialAwareness #SmartMoneyMindset #EmiratesIslamic</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>30 Seconds of Financial Awareness 
-This Global Money Week, remember: small financial habits today can create a stronger future tomorrow.  
-&lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMoneyWeek"&gt;#GlobalMoneyWeek&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialAwareness"&gt;#EIFinancialAwareness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>May 18, 2026 · 5:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-05-18T05:11:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23GlobalMoneyWeek', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialAwareness', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
